--- a/Lauretta_Dataset for Data Analytics-1.xlsx
+++ b/Lauretta_Dataset for Data Analytics-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/C9E79E907B4A7BDA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{FF0C4CF8-31B6-4FC5-8317-36299BA39CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14566B3C-DD02-4C2A-BD64-FAD4A67C66A4}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{FF0C4CF8-31B6-4FC5-8317-36299BA39CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{736052F2-FE6F-4CBF-BD45-F1AF23C6B64C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10834" uniqueCount="4299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10842" uniqueCount="4304">
   <si>
     <t>OrderID</t>
   </si>
@@ -12929,6 +12929,21 @@
   </si>
   <si>
     <t>Zero duplicate rows found</t>
+  </si>
+  <si>
+    <t>Turned this column to proper case</t>
+  </si>
+  <si>
+    <t>CouponCode</t>
+  </si>
+  <si>
+    <t>Used the trim function to remove any white spaces(seen or unseen)</t>
+  </si>
+  <si>
+    <t>Used the PROPER function to make the text even as other columns</t>
+  </si>
+  <si>
+    <t>Resolved all white spaces in all columns</t>
   </si>
 </sst>
 </file>
@@ -13087,7 +13102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -13120,10 +13135,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -13132,63 +13147,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="27">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF999999"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF999999"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -13332,13 +13298,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF999999"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color rgb="FF999999"/>
         </left>
@@ -13351,6 +13310,65 @@
         <bottom style="thin">
           <color rgb="FF999999"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF999999"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF999999"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF999999"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -13646,18 +13664,18 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7E39D21E-8538-4CFD-B3F8-0D225F425DB5}" name="Table2" displayName="Table2" ref="A1:D6" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:D6" xr:uid="{7E39D21E-8538-4CFD-B3F8-0D225F425DB5}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7E39D21E-8538-4CFD-B3F8-0D225F425DB5}" name="Table2" displayName="Table2" ref="A1:D7" totalsRowShown="0" headerRowDxfId="8" dataDxfId="6" headerRowBorderDxfId="7" tableBorderDxfId="5" totalsRowBorderDxfId="4">
+  <autoFilter ref="A1:D7" xr:uid="{7E39D21E-8538-4CFD-B3F8-0D225F425DB5}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="2" xr3:uid="{7DEBCC7C-AD00-404B-BAA0-FEB12B22F81B}" name="Column Affected" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{2F5D38C2-7BB0-4013-96BE-0CC246AE5F23}" name="Description" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{84F84B16-FCB2-48D2-8523-64E30E8AE5B1}" name="Impact" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{943BF78D-FFBC-47B9-9182-ABE880A35371}" name="Status" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{7DEBCC7C-AD00-404B-BAA0-FEB12B22F81B}" name="Column Affected" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{2F5D38C2-7BB0-4013-96BE-0CC246AE5F23}" name="Description" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{84F84B16-FCB2-48D2-8523-64E30E8AE5B1}" name="Impact" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{943BF78D-FFBC-47B9-9182-ABE880A35371}" name="Status" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -66736,7 +66754,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.26953125" customWidth="1"/>
@@ -66760,8 +66778,8 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
-        <v>11</v>
+      <c r="A2" s="20" t="s">
+        <v>4300</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>4288</v>
@@ -66815,16 +66833,39 @@
         <v>4295</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="19"/>
+    <row r="6" spans="1:4" ht="25" x14ac:dyDescent="0.35">
+      <c r="A6" s="18" t="s">
+        <v>4300</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>4302</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>4299</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>4290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="25" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>4296</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>4301</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>4303</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>4290</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>